--- a/Result/profitability/2911.xlsx
+++ b/Result/profitability/2911.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.51</v>
       </c>
       <c r="M2" t="n">
-        <v>0.11</v>
+        <v>0.175</v>
       </c>
       <c r="N2" t="n">
-        <v>38.6625</v>
+        <v>39.26875</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.15</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2975</v>
+        <v>0.33</v>
       </c>
       <c r="N3" t="n">
-        <v>39.96</v>
+        <v>39.855</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.13</v>
       </c>
       <c r="M4" t="n">
-        <v>0.45</v>
+        <v>0.46375</v>
       </c>
       <c r="N4" t="n">
-        <v>39.83375</v>
+        <v>39.9425</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.32</v>
       </c>
       <c r="M5" t="n">
-        <v>0.6075</v>
+        <v>0.635</v>
       </c>
       <c r="N5" t="n">
-        <v>40.14250000000001</v>
+        <v>40.38375</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>0.80875</v>
+        <v>0.8925</v>
       </c>
       <c r="N6" t="n">
-        <v>40.51</v>
+        <v>41.86375</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,13 +1264,13 @@
         <v>0.29</v>
       </c>
       <c r="M7" t="n">
-        <v>1.0325</v>
+        <v>0.22375</v>
       </c>
       <c r="N7" t="n">
-        <v>42.53</v>
+        <v>43.51125</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P7" t="n">
         <v>1</v>
@@ -1282,13 +1282,13 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
         <v>98.2</v>
@@ -1391,13 +1391,13 @@
         <v>0.27</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3612500000000001</v>
+        <v>0.175</v>
       </c>
       <c r="N8" t="n">
-        <v>43.245</v>
+        <v>42.94750000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
@@ -1409,13 +1409,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
         <v>98.3</v>
@@ -2026,10 +2026,10 @@
         <v>0.61</v>
       </c>
       <c r="M13" t="n">
-        <v>0.4475000000000001</v>
+        <v>0.4475</v>
       </c>
       <c r="N13" t="n">
-        <v>44.61624999999999</v>
+        <v>44.61625</v>
       </c>
       <c r="O13" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2911</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>428</v>
+      </c>
+      <c r="D75" t="n">
+        <v>251</v>
+      </c>
+      <c r="E75" t="n">
+        <v>177</v>
+      </c>
+      <c r="F75" t="n">
+        <v>41.32</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-96</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-22.31%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>23</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-73</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-87</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.83</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.0575</v>
+      </c>
+      <c r="N75" t="n">
+        <v>38.43125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-1.49</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-2.257575757575757</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-2.380000000000003</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.05446224256292909</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.2200000000000001</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.2095238095238096</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.04899720741304892</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
